--- a/TuVung/TuVung.xlsx
+++ b/TuVung/TuVung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dxcportal-my.sharepoint.com/personal/dangtan_ngo2_dxc_com/Documents/studyingJapanese/TuVung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43F72557-3246-4E53-B61E-3A0E189E0143}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EBECC4F-AE7C-4470-AFB9-8BAE65A6E81F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0E4D7E1-AC8C-4A97-A943-EDCC3B3B5427}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="1209">
   <si>
     <t>機能</t>
   </si>
@@ -3962,6 +3962,300 @@
     <t>にんしき - NHẬN THỨC - Sự nhận thức
 それでは、VN側はソースだけをリリースすればよい認識でよろしいでしょうか。
 Như vậy, tôi hiểu rằng phía VN chỉ cần release source thôi là được, đúng không ạ?</t>
+  </si>
+  <si>
+    <t>初投稿</t>
+  </si>
+  <si>
+    <t>はつとうこう - SƠ ĐẦU CẢO - File đầu tiên, đóng góp đầu tiên
+初投稿として、資料共有に使用するSharePointを共有します。</t>
+  </si>
+  <si>
+    <t>留意</t>
+  </si>
+  <si>
+    <t>りゅうい / LƯU Ý/ chú ý
+注意 vs 留意
+cả 2 đều mang nghĩa 「気をつけてください」, trong đó 注意 có độ khẩn cấp cao hơn 留意</t>
+  </si>
+  <si>
+    <t>引っ越す</t>
+  </si>
+  <si>
+    <t>ひっこす - DẪN VIỆT- Chuyển (nhà), thay đổi nơi cư trú</t>
+  </si>
+  <si>
+    <t>祝日</t>
+  </si>
+  <si>
+    <t>しゅくじつ - CHÚC NHẬT - Ngày lễ.
+平日： ngày thường (ngày đi làm)
+休日：Ngày nghỉ
+祝日： ngày lễ
+祭日 : ngày đỏ trong lịch, ngày lễ = 祝日</t>
+  </si>
+  <si>
+    <t>仰る</t>
+  </si>
+  <si>
+    <t>おっしゃる - NGƯỠNG- Nói 
+申し上げる：もうしあげる：Khiêm nhường ngữ của 言います。
+申します：もうします：Khiêm nhường ngữ của 言います。
+仰っしゃる：おっしゃいます：Tôn kính ngữ của 言います。</t>
+  </si>
+  <si>
+    <t>提供</t>
+  </si>
+  <si>
+    <t>ていきょう - ĐỀ CUNG-Cung cấp , đưa ra
+お客様のご希望に合った製品をご提供をいたします
+Cung cấp sản phẩm phù hợp với kì vọng của khách hàng</t>
+  </si>
+  <si>
+    <t>キックオフ</t>
+  </si>
+  <si>
+    <t>kick off. Vd: bắt đầu một dự án.</t>
+  </si>
+  <si>
+    <t>要求</t>
+  </si>
+  <si>
+    <t>ようきゅう - YẾU CẦU- yêu cầu bắt buộc
+申請(nhờ vả) =&gt;請求(yêu cầu) =&gt; 要望(nguyện vọng) =&gt; 要求(yêu cầu bắt buộc)</t>
+  </si>
+  <si>
+    <t>認証</t>
+  </si>
+  <si>
+    <t>にんしょう - NHẬN CHỨNG- xác thực /Authentication</t>
+  </si>
+  <si>
+    <t>先出し</t>
+  </si>
+  <si>
+    <t>さきだし - TIÊN XUẤT-Xuất trước</t>
+  </si>
+  <si>
+    <t>続報</t>
+  </si>
+  <si>
+    <t>ぞくほう - TỤC BÁO-thông báo tiếp theo</t>
+  </si>
+  <si>
+    <t>キャンペーン</t>
+  </si>
+  <si>
+    <t>campaign - chiến dịch khuyến mại lớn</t>
+  </si>
+  <si>
+    <t>加盟</t>
+  </si>
+  <si>
+    <t>かめい - GIA MINH -Sự gia nhập; sự tham gia;</t>
+  </si>
+  <si>
+    <t>属性</t>
+  </si>
+  <si>
+    <t>ぞくせい - THUỘC TÍNH -Thuộc tính; phần tử/attribute</t>
+  </si>
+  <si>
+    <t>鉄道</t>
+  </si>
+  <si>
+    <t>てつどう - THIẾT ĐẠO-Đường sắt; đường xe lửa</t>
+  </si>
+  <si>
+    <t>請求</t>
+  </si>
+  <si>
+    <t>せいきゅう - THỈNH CẦU-Sự thỉnh cầu; sự yêu cầu; lời thỉnh cầu
+請求が完了した状態です。Việc thanh toán đã được hoàn tất.</t>
+  </si>
+  <si>
+    <t>残高</t>
+  </si>
+  <si>
+    <t>ざんだか - TÀN CAO-Số dư (ngân hàng)</t>
+  </si>
+  <si>
+    <t>顧客</t>
+  </si>
+  <si>
+    <t>こきゃく - CỐ KHÁCH-khách quen</t>
+  </si>
+  <si>
+    <t>獲得</t>
+  </si>
+  <si>
+    <t>かくとく - HOẠCH ĐẮC-Sự thu được; sự nhận được; sự kiếm được; sự thu nhận, Gặt hái được (sau quá trình cố gắng, nỗ lực).</t>
+  </si>
+  <si>
+    <t>改めて</t>
+  </si>
+  <si>
+    <t>あらためて - CẢI-Một lần nữa, lúc khác,dịp khác lúc khác, 改めてこちらがお訪ねします tôi sẽ đến thăm anh vào dịp khác.</t>
+  </si>
+  <si>
+    <t>厳格</t>
+  </si>
+  <si>
+    <t>げんかく - NGHIÊM CÁCH-Cứng rắn; khắt khe;  nghiêm ngặt</t>
+  </si>
+  <si>
+    <t>徹底</t>
+  </si>
+  <si>
+    <t>てってい - TRIỆT ĐỂ-Sự triệt để (suy nghĩ, thái độ) - Nghiêm túc thực hiện</t>
+  </si>
+  <si>
+    <t>手元</t>
+  </si>
+  <si>
+    <t>てもと - THỦ NGUYÊN-sẵn có</t>
+  </si>
+  <si>
+    <t>落ち度</t>
+  </si>
+  <si>
+    <t>おちど - LẠC ĐỘ-Sai sót, sai lầm</t>
+  </si>
+  <si>
+    <t>文面</t>
+  </si>
+  <si>
+    <t>ぶんめん - VĂN DIỆN-nội dung của bức thư , cốt chuyện , nội dung</t>
+  </si>
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>はんすう - BẢN SỔ-Số phiên bản/version</t>
+  </si>
+  <si>
+    <t>左詰め</t>
+  </si>
+  <si>
+    <t>ひだりづめ - TẢ CẬT-Căn lề trái</t>
+  </si>
+  <si>
+    <t>一律</t>
+  </si>
+  <si>
+    <t>いちりつ - NHẤT LUẬT-Như nhau, Đồng đều; không phân biệt</t>
+  </si>
+  <si>
+    <t>エスケープシーケンス</t>
+  </si>
+  <si>
+    <t>escape sequence - trình tự thoát hiểm</t>
+  </si>
+  <si>
+    <t>外字</t>
+  </si>
+  <si>
+    <t>がいじ - NGOẠI TỰ-External character-Từ vay mượn từ nước ngoài; tiếng nước ngoài;</t>
+  </si>
+  <si>
+    <t>一括</t>
+  </si>
+  <si>
+    <t>いっかつ - NHẤT QUÁT-hàng loạt, Cùng đồng nhất đồng loạt tập trung làm</t>
+  </si>
+  <si>
+    <t>単純</t>
+  </si>
+  <si>
+    <t>たんじゅん - ĐƠN THUẦN-Đơn giản</t>
+  </si>
+  <si>
+    <t>おそらく</t>
+  </si>
+  <si>
+    <t>Có lẽ; = たぶん</t>
+  </si>
+  <si>
+    <t>判明</t>
+  </si>
+  <si>
+    <t>はんめい - PHÁN MINH-làm rõ chân tướng sự việc...hiểu rõ</t>
+  </si>
+  <si>
+    <t>一読</t>
+  </si>
+  <si>
+    <t>いちどく - NHẤT ĐỘC-Xem qua, đọc qua
+一とおり（ざっと）読むこと。</t>
+  </si>
+  <si>
+    <t>単一</t>
+  </si>
+  <si>
+    <t>たんいつ - ĐƠN NHẤT-Đơn nhất; duy nhất,đơn lẻ</t>
+  </si>
+  <si>
+    <t>不適切</t>
+  </si>
+  <si>
+    <t>ふてきせつ - BẤT THÍCH THIẾT-Không phù hợp,không đúng cách</t>
+  </si>
+  <si>
+    <t>ミスリーディング</t>
+  </si>
+  <si>
+    <t>Misleading - Thông tin sai lệch</t>
+  </si>
+  <si>
+    <t>ニュアンス</t>
+  </si>
+  <si>
+    <t>Nuance sắc thái</t>
+  </si>
+  <si>
+    <t>取り掛かる</t>
+  </si>
+  <si>
+    <t>とりかかる -Bắt đầu; bắt tay vào việc
+仕事に取り掛ける. Bắt tay vào công việc.</t>
+  </si>
+  <si>
+    <t>閲覧</t>
+  </si>
+  <si>
+    <t>えつらん - DUYỆT LÃM-đọc 1 cách kỹ lưỡng, thong thả. vừa đọc vừa tìm hiểu.
+資料を閲覧</t>
+  </si>
+  <si>
+    <t>フルパス</t>
+  </si>
+  <si>
+    <t>Full path - đường dẫn</t>
+  </si>
+  <si>
+    <t>プレフィックス</t>
+  </si>
+  <si>
+    <t>prefix - tiền tố</t>
+  </si>
+  <si>
+    <t>突き合わせる</t>
+  </si>
+  <si>
+    <t>つきあわせる - đối sánh, đối chiếu</t>
+  </si>
+  <si>
+    <t>ズレ</t>
+  </si>
+  <si>
+    <t>Sự khác biệt</t>
+  </si>
+  <si>
+    <t>募集</t>
+  </si>
+  <si>
+    <t>ぼしゅう - MỘ TẬP-tuyển dụng
+khác nhau giữa　募集 va 採用 là ·(募集) ``lựa chọn hs tuyển dụng``(採用)``sau khi thi tuyển đã tuyển dụng được ứng viên B ``</t>
   </si>
 </sst>
 </file>
@@ -4440,7 +4734,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572AC1B0-BE23-45AF-BF40-510643C6C658}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B597"/>
+  <dimension ref="A1:B643"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -8990,6 +9284,374 @@
       </c>
       <c r="B597" s="1" t="s">
         <v>1116</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" ht="63">
+      <c r="A598" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" ht="78.75">
+      <c r="A599" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" ht="31.5">
+      <c r="A600" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" ht="94.5">
+      <c r="A601" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" ht="110.25">
+      <c r="A602" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" ht="78.75">
+      <c r="A603" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" ht="63">
+      <c r="A605" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" ht="31.5">
+      <c r="A606" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" ht="31.5">
+      <c r="A610" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" ht="31.5">
+      <c r="A611" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" ht="31.5">
+      <c r="A612" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" ht="63">
+      <c r="A613" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" ht="63">
+      <c r="A616" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" ht="63">
+      <c r="A617" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" ht="31.5">
+      <c r="A618" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" ht="31.5">
+      <c r="A619" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" ht="31.5">
+      <c r="A622" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" ht="31.5">
+      <c r="A625" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" ht="47.25">
+      <c r="A627" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" ht="31.5">
+      <c r="A628" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" ht="31.5">
+      <c r="A631" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" ht="31.5">
+      <c r="A632" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" ht="31.5">
+      <c r="A633" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" ht="31.5">
+      <c r="A634" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" ht="31.5">
+      <c r="A637" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" ht="47.25">
+      <c r="A638" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" ht="78.75">
+      <c r="A643" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>1208</v>
       </c>
     </row>
   </sheetData>

--- a/TuVung/TuVung.xlsx
+++ b/TuVung/TuVung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dxcportal-my.sharepoint.com/personal/dangtan_ngo2_dxc_com/Documents/studyingJapanese/TuVung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EBECC4F-AE7C-4470-AFB9-8BAE65A6E81F}"/>
+  <xr:revisionPtr revIDLastSave="325" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{567D3392-D4C7-4B0E-A1AA-D001D614F982}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0E4D7E1-AC8C-4A97-A943-EDCC3B3B5427}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="1209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="1267">
   <si>
     <t>機能</t>
   </si>
@@ -4256,6 +4256,211 @@
   <si>
     <t>ぼしゅう - MỘ TẬP-tuyển dụng
 khác nhau giữa　募集 va 採用 là ·(募集) ``lựa chọn hs tuyển dụng``(採用)``sau khi thi tuyển đã tuyển dụng được ứng viên B ``</t>
+  </si>
+  <si>
+    <t>助かります</t>
+  </si>
+  <si>
+    <t>たすかる - TRỢ-Được giúp, may quá, đỡ quá. May mà có bạn giúp....
+ご共有いただけますと大変助かります。</t>
+  </si>
+  <si>
+    <t>当初</t>
+  </si>
+  <si>
+    <t>とうしょ - ĐƯƠNG SƠ-Lúc đầu, Mới đầu,Ngay từ đầu</t>
+  </si>
+  <si>
+    <t>特権</t>
+  </si>
+  <si>
+    <t>とっけん - ĐẶC QUYỀN- Đặc quyền,Đặc ân</t>
+  </si>
+  <si>
+    <t>一般</t>
+  </si>
+  <si>
+    <t>いっぱん - NHẤT BÀN-Nói chung, Cái chung; cái thông thường;</t>
+  </si>
+  <si>
+    <t>活用</t>
+  </si>
+  <si>
+    <t>かつよう - HOẠT DỤNG-Sự hoạt dụng; sự sử dụng; sự tận dụng</t>
+  </si>
+  <si>
+    <t>挙動</t>
+  </si>
+  <si>
+    <t>きょどう - CỬ ĐỘNG-Hành động, action,Hành vi</t>
+  </si>
+  <si>
+    <t>従来</t>
+  </si>
+  <si>
+    <t>じゅうらい - TÙNG LAI-Xưa nay, truyền thống, Cho đến giờ; cho tới nay = これまで</t>
+  </si>
+  <si>
+    <t>議論</t>
+  </si>
+  <si>
+    <t>ぎろん - NGHỊ LUẬN - discussion, thảo luận, bàn bạc
+討論 - debate, tranh cãi, tranh luận
+議論 - discussion, thảo luận, bàn bạc</t>
+  </si>
+  <si>
+    <t>選定</t>
+  </si>
+  <si>
+    <t>せんてい - TUYỂN ĐỊNH-Tuyển lựa , tuyển chọn từ một số lượng nhiều ra một vài thứ ưu tú và phù hợp</t>
+  </si>
+  <si>
+    <t>正直</t>
+  </si>
+  <si>
+    <t>しょうじき - CHÁNH TRỰC-Trung thực; thật thà; thành thật</t>
+  </si>
+  <si>
+    <t>小出し</t>
+  </si>
+  <si>
+    <t>こだし - TIỂU XUẤT-(chia từng phần) trong những số lượng nhỏ
+レビューに加わってなるべく小出しで行けるように努めます。
+Tôi sẽ tham gia vào việc review và cố gắng gửi/đưa ra từng phần nhỏ thay vì dồn một lần.
+レビューに加わる
+→ tham gia vào review
+なるべく
+→ cố gắng, trong khả năng có thể
+小出し（こだし）
+→ đưa ra từng ít một, chia nhỏ để cung cấp dần dần
+→ trong dự án thường có nghĩa:
+không đợi hoàn thành hết rồi mới review
+gửi từng phần để review sớm
+行けるように
+→ để có thể thực hiện được
+努めます（つとめます）
+→ sẽ cố gắng</t>
+  </si>
+  <si>
+    <t>プロトタイプ</t>
+  </si>
+  <si>
+    <t>prototype - mô hình thử nghiệm, mẫu thử nghiệm</t>
+  </si>
+  <si>
+    <t>概念</t>
+  </si>
+  <si>
+    <t>がいねん - KHÁI NIỆM-Khái niệm</t>
+  </si>
+  <si>
+    <t>停止</t>
+  </si>
+  <si>
+    <t>ちょうじ - ĐÌNH CHỈ-pause - tạm dừng</t>
+  </si>
+  <si>
+    <t>到着　</t>
+  </si>
+  <si>
+    <t>とうちゃく - ĐÁO TRỨ-Sự đến; sự đến nơi</t>
+  </si>
+  <si>
+    <t>次第</t>
+  </si>
+  <si>
+    <t>しだい - THỨ ĐỆ-1.Do đó, vì vậy, 2.Ngay sau khi,3. Tùy ở N
+3 nghĩa thông dụng:
+1. V-る/V-た + 次第だ: Do đó, vì vậy (次第 hay ở cuối câu)
+2. Vます+次第: Ngay sau khi
+3. N + 次第: Tùy ở N
+定例会が終わり次第説明会の会議に切り替えるでもOKです。
+Sau khi cuộc họp định kỳ (定例会) kết thúc, chuyển sang cuộc họp giải thích/trao đổi (説明会) cũng được.
+Phân tích từ vựng
+定例会（ていれいかい）: cuộc họp định kỳ
+終わり次第（おわりしだい）: ngay sau khi kết thúc
+説明会（せつめいかい）: buổi giải thích, buổi giới thiệu, buổi briefing
+切り替える（きりかえる）: chuyển đổi, chuyển sang
+～でもOKです: cũng được, không vấn đề gì</t>
+  </si>
+  <si>
+    <t>サンプル</t>
+  </si>
+  <si>
+    <t>sample, mẫu</t>
+  </si>
+  <si>
+    <t>枠線</t>
+  </si>
+  <si>
+    <t>わくせん - TUYẾN-Border, khung (trong excel)</t>
+  </si>
+  <si>
+    <t>箇条書</t>
+  </si>
+  <si>
+    <t>かじょうがき - CÁ ĐIỀU THƯ-Ghi thành ý chính (gạch đầu dòng)</t>
+  </si>
+  <si>
+    <t>充てる</t>
+  </si>
+  <si>
+    <t>あてる - SUNG-phân bổ vào</t>
+  </si>
+  <si>
+    <t>オートサイズ</t>
+  </si>
+  <si>
+    <t>Auto Size -Tự động điều chỉnh kích thước</t>
+  </si>
+  <si>
+    <t>拡大縮小</t>
+  </si>
+  <si>
+    <t>かくだいしゅくしょう - KHUẾCH ĐẠI SÚC TIỂU-Mở rộng và thu hẹp/rescale</t>
+  </si>
+  <si>
+    <t>独自</t>
+  </si>
+  <si>
+    <t>どくじ - ĐỘC TỰ-Riêng; cá nhân</t>
+  </si>
+  <si>
+    <t>精度</t>
+  </si>
+  <si>
+    <t>せいど - TINH ĐỘ-Độ chính xác</t>
+  </si>
+  <si>
+    <t>問合せ</t>
+  </si>
+  <si>
+    <t>といあわせ - VẤN HỢP-sự tìm hiểu thông tin; sự thắc mắc</t>
+  </si>
+  <si>
+    <t>違和感</t>
+  </si>
+  <si>
+    <t>いわかん - VI HÒA CẢM-Có cảm giác không hợp, Lạ, kì lạ.</t>
+  </si>
+  <si>
+    <t>貰う</t>
+  </si>
+  <si>
+    <t>もらう - THẾ-nhận (từ người khác thành của mk)
+kính ngữ của もらいます là おおさめになります</t>
+  </si>
+  <si>
+    <t>先程</t>
+  </si>
+  <si>
+    <t>さきほど - TIÊN TRÌNH-vừa lúc nãy (lịch sự hơn さっき)</t>
+  </si>
+  <si>
+    <t>対照</t>
+  </si>
+  <si>
+    <t>たいしょう - ĐỐI CHIẾU-Sự đối chiếu.1. đối chiếu so sánh, 2. tương phản</t>
   </si>
 </sst>
 </file>
@@ -4734,7 +4939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572AC1B0-BE23-45AF-BF40-510643C6C658}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B643"/>
+  <dimension ref="A1:B672"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -9652,6 +9857,238 @@
       </c>
       <c r="B643" s="1" t="s">
         <v>1208</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" ht="47.25">
+      <c r="A644" s="11" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" ht="31.5">
+      <c r="A645" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" ht="31.5">
+      <c r="A647" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" ht="31.5">
+      <c r="A648" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" ht="31.5">
+      <c r="A649" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" ht="47.25">
+      <c r="A650" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" ht="63">
+      <c r="A651" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" ht="47.25">
+      <c r="A652" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" ht="31.5">
+      <c r="A653" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" ht="346.5">
+      <c r="A654" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" ht="31.5">
+      <c r="A655" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" ht="346.5">
+      <c r="A659" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" ht="31.5">
+      <c r="A661" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" ht="31.5">
+      <c r="A662" s="9" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" ht="31.5">
+      <c r="A664" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" ht="31.5">
+      <c r="A665" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" ht="31.5">
+      <c r="A668" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" ht="31.5">
+      <c r="A669" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" ht="47.25">
+      <c r="A670" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" ht="31.5">
+      <c r="A671" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" ht="31.5">
+      <c r="A672" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>1266</v>
       </c>
     </row>
   </sheetData>

--- a/TuVung/TuVung.xlsx
+++ b/TuVung/TuVung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dxcportal-my.sharepoint.com/personal/dangtan_ngo2_dxc_com/Documents/studyingJapanese/TuVung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="325" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{567D3392-D4C7-4B0E-A1AA-D001D614F982}"/>
+  <xr:revisionPtr revIDLastSave="408" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10AE96A3-17C1-4782-AE6D-5CA8FA64F8EC}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0E4D7E1-AC8C-4A97-A943-EDCC3B3B5427}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="1267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="1333">
   <si>
     <t>機能</t>
   </si>
@@ -4461,6 +4461,207 @@
   </si>
   <si>
     <t>たいしょう - ĐỐI CHIẾU-Sự đối chiếu.1. đối chiếu so sánh, 2. tương phản</t>
+  </si>
+  <si>
+    <t>トリガー</t>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
+    <t>格納</t>
+  </si>
+  <si>
+    <t>かくのう - CÁCH NẠP- Lưu trữ/save</t>
+  </si>
+  <si>
+    <t>マニフェストリポジトリ</t>
+  </si>
+  <si>
+    <t>Manifest Repository - Kho lưu trữ Manifest</t>
+  </si>
+  <si>
+    <t>マージ</t>
+  </si>
+  <si>
+    <t>merge - hợp nhất làm 1</t>
+  </si>
+  <si>
+    <t>コンテナイメージ</t>
+  </si>
+  <si>
+    <t>Container image</t>
+  </si>
+  <si>
+    <t>タグ</t>
+  </si>
+  <si>
+    <t>tag - stagingタグ</t>
+  </si>
+  <si>
+    <t>検出</t>
+  </si>
+  <si>
+    <t>けんしゅつ - KIỂM XUẤT- phát hiện, dò tìm</t>
+  </si>
+  <si>
+    <t>インベントリファイル</t>
+  </si>
+  <si>
+    <t>Inventory file - Tệp kiểm kê</t>
+  </si>
+  <si>
+    <t>プッシュ</t>
+  </si>
+  <si>
+    <t>push</t>
+  </si>
+  <si>
+    <t>シークレット</t>
+  </si>
+  <si>
+    <t>secret - bí mật</t>
+  </si>
+  <si>
+    <t>秘密鍵</t>
+  </si>
+  <si>
+    <t>ひみつかぎ - BÍ MẬT KIỆN-Khóa riêng /secret key</t>
+  </si>
+  <si>
+    <t>除去</t>
+  </si>
+  <si>
+    <t>じょきょ - TRỪ KHỨ- Loại bỏ</t>
+  </si>
+  <si>
+    <t>払い出す</t>
+  </si>
+  <si>
+    <t>はらいだす - PHẤT XUẤT- Trả tiền, thanh toán; đuổi đi, xua đuổi</t>
+  </si>
+  <si>
+    <t>スロット</t>
+  </si>
+  <si>
+    <t>slot - chỗ</t>
+  </si>
+  <si>
+    <t>ゼロダウンタイム</t>
+  </si>
+  <si>
+    <t>Zero downtime / Không gián đoạn</t>
+  </si>
+  <si>
+    <t>アーキテクチャ</t>
+  </si>
+  <si>
+    <t>architecture / kiến ​​​​trúc hệ thống</t>
+  </si>
+  <si>
+    <t>コンポーネント</t>
+  </si>
+  <si>
+    <t>component /thành phần</t>
+  </si>
+  <si>
+    <t>付与</t>
+  </si>
+  <si>
+    <t>ふよ - PHÓ DỮ- cấp,gán (quyền)</t>
+  </si>
+  <si>
+    <t>回避</t>
+  </si>
+  <si>
+    <t>かいひ - HỒI TỊ- Sự tránh; sự tránh né
+リスクを回避する： Tránh rủi ro</t>
+  </si>
+  <si>
+    <t>遮断</t>
+  </si>
+  <si>
+    <t xml:space="preserve">しゃだん - GIÀ ĐOẠN- ngăn cách, ngắt </t>
+  </si>
+  <si>
+    <t>定常</t>
+  </si>
+  <si>
+    <t>ていじょう - ĐỊNH THƯỜNG- Trạng thái ổn định</t>
+  </si>
+  <si>
+    <t>人手</t>
+  </si>
+  <si>
+    <t>ひとで - NHÂN THỦ- Tay người; số người làm</t>
+  </si>
+  <si>
+    <t>介在</t>
+  </si>
+  <si>
+    <t>かいざい - GIỚI TẠI- Trung gian hoà giải; can thiệp</t>
+  </si>
+  <si>
+    <t>鍵</t>
+  </si>
+  <si>
+    <t>かぎ - KIỆN- Chìa khóa / key</t>
+  </si>
+  <si>
+    <t>公開鍵</t>
+  </si>
+  <si>
+    <t>こうかいかぎ - CÔNG KHAI KIỆN- Khóa công khai/ public key</t>
+  </si>
+  <si>
+    <t>採用</t>
+  </si>
+  <si>
+    <t>さいよう - THẢI DỤNG- sử dụng, chấp nhận</t>
+  </si>
+  <si>
+    <t>論点</t>
+  </si>
+  <si>
+    <t>ろんてん - LUẬN ĐIỂM - Vấn đề chính</t>
+  </si>
+  <si>
+    <t>コネクションキャッシュ</t>
+  </si>
+  <si>
+    <t>Connection cache - bộ nhớ đệm kết nối</t>
+  </si>
+  <si>
+    <t>懸念</t>
+  </si>
+  <si>
+    <t>けねん - HUYỀN NIỆM- quan ngại, lo lắng</t>
+  </si>
+  <si>
+    <t>洗い出し</t>
+  </si>
+  <si>
+    <t>あらいだし - TẨY XUẤT- tìm và đưa ra (vấn đề để giải quyết)</t>
+  </si>
+  <si>
+    <t>早期</t>
+  </si>
+  <si>
+    <t>そうき - TẢO KÌ-  thời kỳ đầu, Giai đoạn đầu
+早期発見: phát hiện sớm</t>
+  </si>
+  <si>
+    <t>詰まり</t>
+  </si>
+  <si>
+    <t>つまり - CẬT- Trạng từ: Nói cách khác,Tóm lại; rốt cuộc là
+Danh từ: Sự tắc; việc bị nghẹt, Hồi kết; kết cục</t>
+  </si>
+  <si>
+    <t>破壊</t>
+  </si>
+  <si>
+    <t>はかい - PHÁ HOẠI- phá hoại, phá hủy</t>
   </si>
 </sst>
 </file>
@@ -4939,7 +5140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572AC1B0-BE23-45AF-BF40-510643C6C658}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B672"/>
+  <dimension ref="A1:B705"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -10089,6 +10290,270 @@
       </c>
       <c r="B672" s="1" t="s">
         <v>1266</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" s="11" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" ht="31.5">
+      <c r="A675" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" ht="31.5">
+      <c r="A679" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" ht="31.5">
+      <c r="A683" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2" ht="31.5">
+      <c r="A685" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2" ht="31.5">
+      <c r="A691" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2" ht="31.5">
+      <c r="A693" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2" ht="31.5">
+      <c r="A694" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2" ht="31.5">
+      <c r="A695" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2" ht="31.5">
+      <c r="A697" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2" ht="31.5">
+      <c r="A698" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2" ht="31.5">
+      <c r="A702" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2" ht="47.25">
+      <c r="A703" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2" ht="63">
+      <c r="A704" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>1332</v>
       </c>
     </row>
   </sheetData>

--- a/TuVung/TuVung.xlsx
+++ b/TuVung/TuVung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dxcportal-my.sharepoint.com/personal/dangtan_ngo2_dxc_com/Documents/studyingJapanese/TuVung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="408" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10AE96A3-17C1-4782-AE6D-5CA8FA64F8EC}"/>
+  <xr:revisionPtr revIDLastSave="557" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2763429-DCD6-4CCE-A670-E08B3994C5D1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0E4D7E1-AC8C-4A97-A943-EDCC3B3B5427}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="1333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="1407">
   <si>
     <t>機能</t>
   </si>
@@ -4662,6 +4662,247 @@
   </si>
   <si>
     <t>はかい - PHÁ HOẠI- phá hoại, phá hủy</t>
+  </si>
+  <si>
+    <t>層</t>
+  </si>
+  <si>
+    <t>そう - TẰNG- Đếm tầng, lớp : いっそう、にそう、さんそう</t>
+  </si>
+  <si>
+    <t>齟齬</t>
+  </si>
+  <si>
+    <t>そご - TRỞ NGỮ- sự mâu thuẫn,xung đột/ conflict</t>
+  </si>
+  <si>
+    <t>急務</t>
+  </si>
+  <si>
+    <t>きゅうむ - CẤP VỤ- Công việc khẩn cấp; nhiệm vụ cấp bách</t>
+  </si>
+  <si>
+    <t>途中</t>
+  </si>
+  <si>
+    <t>とちゅう - ĐỒ TRUNG- Dọc đường, Giữa chừng, Nửa đường</t>
+  </si>
+  <si>
+    <t>フィードバック</t>
+  </si>
+  <si>
+    <t>feedback - nhận xét</t>
+  </si>
+  <si>
+    <t>遅延</t>
+  </si>
+  <si>
+    <t>ちえん - TRÌ DUYÊN- trì hoãn</t>
+  </si>
+  <si>
+    <t>模擬</t>
+  </si>
+  <si>
+    <t>もぎ - MÔ NGHĨ- mô phỏng, bắt chước</t>
+  </si>
+  <si>
+    <t>避ける</t>
+  </si>
+  <si>
+    <t>よける - TỊ- ①さける Tránh né, trốn tránh ( trách nhiệm, mối nguy hiểm...)
+②よける　Phòng tránh ( côn trùng, bệnh...)</t>
+  </si>
+  <si>
+    <t>承認</t>
+  </si>
+  <si>
+    <t>しょうにん - THỪA NHẬN- sự xác nhận, phê duyệt</t>
+  </si>
+  <si>
+    <t>一環</t>
+  </si>
+  <si>
+    <t>いっかん - NHẤT HOÀN- 1 phần trong
+仕事の一環: một phần công việc.</t>
+  </si>
+  <si>
+    <t>真</t>
+  </si>
+  <si>
+    <t>まな - CHÂN- thật, thực tế
+真のURL:URL thật / URL thực tế / URL chính thức</t>
+  </si>
+  <si>
+    <t>同感</t>
+  </si>
+  <si>
+    <t>どうかん - ĐỒNG CẢM- Sự cùng ý kiến; sự cùng suy nghĩ
+同情：hán tự là đồng tình nhưng ý nghĩa là đồng cảm, cảm thương trước khó khăn của người khác
+同感：hán tự là đồng cảm nhưng ý nghĩa là đồng tình, cùng ý kiến với người khác</t>
+  </si>
+  <si>
+    <t>繋い</t>
+  </si>
+  <si>
+    <t>つなぐ - HỆ- Buộc vào; thắt; kết nối.
+インターネットを繋ぐkết nối internet</t>
+  </si>
+  <si>
+    <t>高負荷</t>
+  </si>
+  <si>
+    <t>こうふか - CAO PHỤ HÀ- Cường độ cao
+IT: 高負荷の処理: những xử lý nặng của máy tính.</t>
+  </si>
+  <si>
+    <t>並走</t>
+  </si>
+  <si>
+    <t>へいそう - TỊNH TẨU- Chạy song song</t>
+  </si>
+  <si>
+    <t>無限</t>
+  </si>
+  <si>
+    <t>むげん - VÔ HẠN- Sự vô hạn
+無限列車篇　chuyến tàu vô tận</t>
+  </si>
+  <si>
+    <t>過渡</t>
+  </si>
+  <si>
+    <t>かと - QUÁ ĐỘ- Giai đoạn chuyển tiếp (transition period) hoặc trạng thái quá độ</t>
+  </si>
+  <si>
+    <t>突合</t>
+  </si>
+  <si>
+    <t>つきあわせ - ĐỘT HỢP- matching: phù hợp.(member matching DB)</t>
+  </si>
+  <si>
+    <t>見落</t>
+  </si>
+  <si>
+    <t>みおとし - KIẾN LẠC- Nhìn sót, bỏ sót, không nhận thấy
+メッセージを見落としていました : Tôi đã bỏ sót tin nhắn</t>
+  </si>
+  <si>
+    <t>一歩一歩</t>
+  </si>
+  <si>
+    <t>いっぽいっぽ - NHẤT BỘ NHẤT BỘ- Từng bước. Step by step</t>
+  </si>
+  <si>
+    <t>スレッド</t>
+  </si>
+  <si>
+    <t>thread - chủ đề</t>
+  </si>
+  <si>
+    <t>共用</t>
+  </si>
+  <si>
+    <t>きょうよう - CỘNG DỤNG- Sự cùng nhau sử dụng; sự dùng chung;</t>
+  </si>
+  <si>
+    <t>素早く</t>
+  </si>
+  <si>
+    <t>すばやく - TỐ TẢO- Nhanh, nhanh chóng, Lẹ làng, lanh lợi</t>
+  </si>
+  <si>
+    <t>余裕</t>
+  </si>
+  <si>
+    <t>よゆう - DƯ DỤ- Dư thừa, rộng rãi,sớm hơn
+余裕を持って来るように。hãy cố gắng đến sớm hơn</t>
+  </si>
+  <si>
+    <t>順次</t>
+  </si>
+  <si>
+    <t>じゅんじ- THUẬN THỨ- Tuần tự, lần lượt
+Có mấy từ gần nghĩa với nhau là:
+順次、順番、逐次</t>
+  </si>
+  <si>
+    <t>丁寧</t>
+  </si>
+  <si>
+    <t>ていねい - ĐINH NINH- Sự lịch sự; sự cẩn thận.
+丁寧にありがとうございます。</t>
+  </si>
+  <si>
+    <t>十分</t>
+  </si>
+  <si>
+    <t>じゅうぶん - THẬP PHÂN- Đầy đủ; hoàn toàn; chặt chẽ; sít sao; rõ</t>
+  </si>
+  <si>
+    <t>軽微</t>
+  </si>
+  <si>
+    <t>けいび - KHINH VI- không đáng kể, nhỏ</t>
+  </si>
+  <si>
+    <t>迅速</t>
+  </si>
+  <si>
+    <t>じんそく - TẤN TỐC- Sự mau lẹ; sự nhanh chóng.
+迅速なご対応助かりました。</t>
+  </si>
+  <si>
+    <t>コロコロ</t>
+  </si>
+  <si>
+    <t>xoành xoạch
+コロコロ変化する: thay đổi xoành xoạch</t>
+  </si>
+  <si>
+    <t>協力</t>
+  </si>
+  <si>
+    <t>きょうりょく - HIỆP LỰC- Sự hợp tác; hợp tác; sự hiệp lực; hiệp lực
+1。能力(のうりょく)năng lực
+2。努力(どりょく)nỗ lực
+3。協力(きょうりょく)chung sức, hợp tác , hiệp lực</t>
+  </si>
+  <si>
+    <t>一部</t>
+  </si>
+  <si>
+    <t>いちぶ - NHẤT BỘ- Một phần</t>
+  </si>
+  <si>
+    <t>混乱</t>
+  </si>
+  <si>
+    <t>こんらん - HỖN LOẠN- Lúng túng; hỗn loạn</t>
+  </si>
+  <si>
+    <t>大量</t>
+  </si>
+  <si>
+    <t>たいりょう - ĐẠI LƯỢNG- Số lượng lớn</t>
+  </si>
+  <si>
+    <t>増強</t>
+  </si>
+  <si>
+    <t>ぞうきょう - TĂNG CƯỜNG- Tăng cường củng cố</t>
+  </si>
+  <si>
+    <t>賄う</t>
+  </si>
+  <si>
+    <t>まかなう - HỐI- Nghĩa 1: trang trải, chi trả, ...
+Nghĩa 2: cung cấp</t>
+  </si>
+  <si>
+    <t>段階</t>
+  </si>
+  <si>
+    <t>きだはし - ĐOẠN GIAI- các bước, giai đoạn</t>
   </si>
 </sst>
 </file>
@@ -5140,7 +5381,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572AC1B0-BE23-45AF-BF40-510643C6C658}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B742"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -10554,6 +10795,302 @@
       </c>
       <c r="B705" s="1" t="s">
         <v>1332</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" ht="31.5">
+      <c r="A706" s="11" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" ht="31.5">
+      <c r="A707" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" ht="31.5">
+      <c r="A708" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2" ht="31.5">
+      <c r="A709" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2" ht="63">
+      <c r="A713" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2" ht="31.5">
+      <c r="A714" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2" ht="31.5">
+      <c r="A715" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2" ht="47.25">
+      <c r="A716" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2" ht="126">
+      <c r="A717" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2" ht="31.5">
+      <c r="A718" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2" ht="47.25">
+      <c r="A719" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" ht="31.5">
+      <c r="A721" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" ht="47.25">
+      <c r="A722" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" ht="31.5">
+      <c r="A723" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2" ht="63">
+      <c r="A724" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" ht="31.5">
+      <c r="A725" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" ht="31.5">
+      <c r="A727" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2" ht="31.5">
+      <c r="A728" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2" ht="63">
+      <c r="A729" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" ht="47.25">
+      <c r="A730" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2" ht="47.25">
+      <c r="A731" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" ht="31.5">
+      <c r="A732" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" ht="47.25">
+      <c r="A734" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" ht="31.5">
+      <c r="A735" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" ht="94.5">
+      <c r="A736" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" ht="31.5">
+      <c r="A738" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" ht="31.5">
+      <c r="A740" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B740" s="1" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" ht="47.25">
+      <c r="A741" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" ht="31.5">
+      <c r="A742" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B742" s="1" t="s">
+        <v>1406</v>
       </c>
     </row>
   </sheetData>

--- a/TuVung/TuVung.xlsx
+++ b/TuVung/TuVung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dxcportal-my.sharepoint.com/personal/dangtan_ngo2_dxc_com/Documents/studyingJapanese/TuVung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="557" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2763429-DCD6-4CCE-A670-E08B3994C5D1}"/>
+  <xr:revisionPtr revIDLastSave="683" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43FD95E8-C2B5-463E-A13C-5747813B7433}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0E4D7E1-AC8C-4A97-A943-EDCC3B3B5427}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0E4D7E1-AC8C-4A97-A943-EDCC3B3B5427}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$574</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1" iterateCount="10"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="1407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="1495">
   <si>
     <t>機能</t>
   </si>
@@ -4903,6 +4903,282 @@
   </si>
   <si>
     <t>きだはし - ĐOẠN GIAI- các bước, giai đoạn</t>
+  </si>
+  <si>
+    <t>成果</t>
+  </si>
+  <si>
+    <t>せいか - THÀNH QUẢ- Thành quả; kết quả./outcome</t>
+  </si>
+  <si>
+    <t>棚卸</t>
+  </si>
+  <si>
+    <t>たなおろし - BẰNG TÁ- Kiểm kê./Check hàng tồn kho
+棚卸済
+Đã kiểm kê xong</t>
+  </si>
+  <si>
+    <t>月頃</t>
+  </si>
+  <si>
+    <t>つきごろ - NGUYỆT KHOẢNH- mỗi tháng</t>
+  </si>
+  <si>
+    <t>拝見</t>
+  </si>
+  <si>
+    <t>はいけん - BÁI KIẾN- 見る：xem, nhìn thấy
+- Tôn kính ngữ: ご覧になります（ごらんになります）
+- Khiêm nhường ngữ: 拝見します</t>
+  </si>
+  <si>
+    <t>おっしゃる</t>
+  </si>
+  <si>
+    <t>仰る - おっしゃる - Nói cho biết
+おっしゃる通り: đúng như bạn nói</t>
+  </si>
+  <si>
+    <t>相違</t>
+  </si>
+  <si>
+    <t>そうい - TƯƠNG VI- Sự khác nhau giữa 2 cái</t>
+  </si>
+  <si>
+    <t>少々</t>
+  </si>
+  <si>
+    <t>しょうしょう - THIỂU- Một chút; một lát</t>
+  </si>
+  <si>
+    <t>非同期</t>
+  </si>
+  <si>
+    <t>ひどうき - PHI ĐỒNG KÌ- lập trình: bất đồng bộ
+Không đồng bộ</t>
+  </si>
+  <si>
+    <t>状態</t>
+  </si>
+  <si>
+    <t>じょうたい - TRẠNG THÁI- Tình trạng/ trạng thái ☆状態が良いです</t>
+  </si>
+  <si>
+    <t>見立て</t>
+  </si>
+  <si>
+    <t>みたて - KIẾN LẬP- Xem và lựa chọn</t>
+  </si>
+  <si>
+    <t>差し上げ</t>
+  </si>
+  <si>
+    <t>さしあげ - SOA THƯỢNG- Giúp, hỗ trợ…</t>
+  </si>
+  <si>
+    <t>カバー</t>
+  </si>
+  <si>
+    <t>cover - bao phủ/ che phủ</t>
+  </si>
+  <si>
+    <t>類似</t>
+  </si>
+  <si>
+    <t>るいじ - LOẠI TỰ- Sự tương tự; sự giống nhau</t>
+  </si>
+  <si>
+    <t>不備</t>
+  </si>
+  <si>
+    <t>ふび - BẤT BỊ- Thiếu sót, Không hoàn chỉnh; không vẹn toàn</t>
+  </si>
+  <si>
+    <t>新設</t>
+  </si>
+  <si>
+    <t>しんせつ - TÂN THIẾT- Sự thành lập mới; sự thiết lập mới;</t>
+  </si>
+  <si>
+    <t>介して</t>
+  </si>
+  <si>
+    <t>かいして - GIỚI- Thông qua, qua (Thông qua vật trung gian nào đó thì dùng từ này)</t>
+  </si>
+  <si>
+    <t>元々</t>
+  </si>
+  <si>
+    <t>もともと - NGUYÊN- Vốn dĩ; nguyên là; vốn là.</t>
+  </si>
+  <si>
+    <t>共有</t>
+  </si>
+  <si>
+    <t>きょうゆう - CỘNG HỮU- cùng chia sẻ/ share</t>
+  </si>
+  <si>
+    <t>後続</t>
+  </si>
+  <si>
+    <t>こうぞく - HẬU TỤC- Phía sau
+Phía sau. Ví dụ: 後続車 (Xe phía sau)</t>
+  </si>
+  <si>
+    <t>危険</t>
+  </si>
+  <si>
+    <t>きけん - NGUY HIỂM- Sự nguy hiểm; mối nguy hiểm</t>
+  </si>
+  <si>
+    <t>準備</t>
+  </si>
+  <si>
+    <t>じゅんび - CHUẨN BỊ- Sự chuẩn bị; sự sắp xếp;</t>
+  </si>
+  <si>
+    <t>両者</t>
+  </si>
+  <si>
+    <t>りょうしゃ - LƯỠNG GIẢ- Cả 2 người. Cả 2 thứ. Cả 2 cái</t>
+  </si>
+  <si>
+    <t>挙げて</t>
+  </si>
+  <si>
+    <t>あげて - CỬ- đưa ra, nêu ra (vấn đề)</t>
+  </si>
+  <si>
+    <t>臨時</t>
+  </si>
+  <si>
+    <t>りんじ - LÂM THÌ- Lâm thời, tạm thời</t>
+  </si>
+  <si>
+    <t>引き渡す</t>
+  </si>
+  <si>
+    <t>ひきわたす- DẪN ĐỘ- bàn giao công việc: 仕事を引き渡す</t>
+  </si>
+  <si>
+    <t>可視</t>
+  </si>
+  <si>
+    <t>かし - KHẢ THỊ- rõ ràng
+可視のミス：Lỗi rõ ràng</t>
+  </si>
+  <si>
+    <t>有効</t>
+  </si>
+  <si>
+    <t>ゆうこう - HỮU HIỆU- Hữu hiệu; có hiệu quả</t>
+  </si>
+  <si>
+    <t>前者</t>
+  </si>
+  <si>
+    <t>ぜんしゃ - TIỀN GIẢ- Người lúc trước; điều thứ nhất; người trước
+後者:nghĩa của từ này là chỉ : Người sau, Cái sau, cái cuối cùng
+前者: nghĩa của từ này là chỉ : Người đầu tiên, thứ đầu tiền, cái đầu tiên</t>
+  </si>
+  <si>
+    <t>話題</t>
+  </si>
+  <si>
+    <t>わだい - THOẠI ĐỀ- Chủ đề, đề tài</t>
+  </si>
+  <si>
+    <t>原則</t>
+  </si>
+  <si>
+    <t>げんそく - NGUYÊN TẮC- Nguyên tắc; quy tắc chung</t>
+  </si>
+  <si>
+    <t>送付</t>
+  </si>
+  <si>
+    <t>そうふ - TỐNG PHÓ- Việc gửi; việc chuyển</t>
+  </si>
+  <si>
+    <t>受付</t>
+  </si>
+  <si>
+    <t>うけつけ - THỤ PHÓ- Sự tiếp thu; sự tiếp nhận;</t>
+  </si>
+  <si>
+    <t>申込</t>
+  </si>
+  <si>
+    <t>もうしこみ - THÂN NHẬP - đăng ký</t>
+  </si>
+  <si>
+    <t>郵便</t>
+  </si>
+  <si>
+    <t>ゆうびん - BƯU TIỆN- Bưu điện; dịch vụ bưu điện./mail ( service)</t>
+  </si>
+  <si>
+    <t>脱会</t>
+  </si>
+  <si>
+    <t>だっかい - THOÁT HỘI- rút khỏi, thôi tham gia hội/nhóm, hủy tư cách thành viên.</t>
+  </si>
+  <si>
+    <t>届出</t>
+  </si>
+  <si>
+    <t>とどけで - GIỚI XUẤT- Bản báo cáo, tường trình, khai báo</t>
+  </si>
+  <si>
+    <t>特約</t>
+  </si>
+  <si>
+    <t>とくやく - ĐẶC ƯỚC- Hợp đồng đặc biệt.</t>
+  </si>
+  <si>
+    <t>紛失</t>
+  </si>
+  <si>
+    <t>ふんしつ - PHÂN THẤT- Việc làm mất; việc đánh mất</t>
+  </si>
+  <si>
+    <t>盗難</t>
+  </si>
+  <si>
+    <t>とうなん - ĐẠO NAN- Vụ trộm; vụ ăn cắp</t>
+  </si>
+  <si>
+    <t>基幹</t>
+  </si>
+  <si>
+    <t>きかん - CƠ CÁN- Trụ cột chính; hạt nhân; điều cốt yếu
+基幹システム：hệ thống cốt lõi (core system: IT)</t>
+  </si>
+  <si>
+    <t>タイムスタンプ</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>エンボス</t>
+  </si>
+  <si>
+    <t>Embossing - chữ nổi, ký tự được dập nổi.
+エンボスローマ字: Tên bằng chữ La-tinh được dập nổi trên thẻ.</t>
+  </si>
+  <si>
+    <t>入会</t>
+  </si>
+  <si>
+    <t>いりあい - NHẬP HỘI- tham gia, gia nhập hội, câu lạc bộ</t>
+  </si>
+  <si>
+    <t>金融機関</t>
+  </si>
+  <si>
+    <t>きんゆうきかん - KIM DUNG KI QUAN- Tổ chức tín dụng, tổ chức tài chính</t>
   </si>
 </sst>
 </file>
@@ -5381,7 +5657,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572AC1B0-BE23-45AF-BF40-510643C6C658}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B742"/>
+  <dimension ref="A1:B786"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -9253,7 +9529,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="513" spans="1:2" ht="31.5">
+    <row r="513" spans="1:2">
       <c r="A513" s="2" t="s">
         <v>955</v>
       </c>
@@ -11093,12 +11369,364 @@
         <v>1406</v>
       </c>
     </row>
+    <row r="743" spans="1:2" ht="31.5">
+      <c r="A743" s="11" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" ht="63">
+      <c r="A744" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" ht="78.75">
+      <c r="A746" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" ht="31.5">
+      <c r="A747" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" ht="31.5">
+      <c r="A748" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B748" s="1" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" ht="47.25">
+      <c r="A750" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" ht="31.5">
+      <c r="A751" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" ht="31.5">
+      <c r="A755" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B755" s="1" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" ht="31.5">
+      <c r="A756" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B756" s="1" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" ht="31.5">
+      <c r="A757" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" ht="47.25">
+      <c r="A758" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" ht="31.5">
+      <c r="A759" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" ht="31.5">
+      <c r="A760" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" ht="31.5">
+      <c r="A761" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" ht="31.5">
+      <c r="A762" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" ht="31.5">
+      <c r="A763" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" ht="31.5">
+      <c r="A764" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" ht="31.5">
+      <c r="A767" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" ht="31.5">
+      <c r="A768" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" ht="31.5">
+      <c r="A769" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" ht="94.5">
+      <c r="A770" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" ht="31.5">
+      <c r="A772" s="11" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2" ht="31.5">
+      <c r="A773" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" ht="31.5">
+      <c r="A774" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" ht="31.5">
+      <c r="A776" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" ht="47.25">
+      <c r="A777" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" ht="31.5">
+      <c r="A778" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" ht="31.5">
+      <c r="A780" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" ht="63">
+      <c r="A782" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" ht="63">
+      <c r="A784" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" ht="31.5">
+      <c r="A785" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" ht="31.5">
+      <c r="A786" s="8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B574" xr:uid="{572AC1B0-BE23-45AF-BF40-510643C6C658}"/>
-  <conditionalFormatting sqref="A1:A558 A560:A1048576">
+  <conditionalFormatting sqref="A1:A558 A560:A785 A787:A1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A485:A505 A1:A483 A507:A558 A560:A1048576">
+  <conditionalFormatting sqref="A485:A505 A1:A483 A507:A558 A560:A785 A787:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>

--- a/TuVung/TuVung.xlsx
+++ b/TuVung/TuVung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dxcportal-my.sharepoint.com/personal/dangtan_ngo2_dxc_com/Documents/studyingJapanese/TuVung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="683" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43FD95E8-C2B5-463E-A13C-5747813B7433}"/>
+  <xr:revisionPtr revIDLastSave="839" documentId="13_ncr:1_{AD9B2405-E9FD-4D4A-80B7-293F6A025480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8156ADC7-B663-4244-8E6B-96DDF066E7CE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0E4D7E1-AC8C-4A97-A943-EDCC3B3B5427}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="1495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="1593">
   <si>
     <t>機能</t>
   </si>
@@ -5179,6 +5179,356 @@
   </si>
   <si>
     <t>きんゆうきかん - KIM DUNG KI QUAN- Tổ chức tín dụng, tổ chức tài chính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+契約割販</t>
+  </si>
+  <si>
+    <t>けいやくかっぱん ( Khế Ước Cát Phiến) Hợp đồng trả góp</t>
+  </si>
+  <si>
+    <t>読み込み</t>
+  </si>
+  <si>
+    <t>よみこみ - ĐỘC NHẬP - Load / đọc, tải
+読み込み中: loading</t>
+  </si>
+  <si>
+    <t>過程</t>
+  </si>
+  <si>
+    <t>かてい - QUÁ TRÌNH- Quá trình; giai đoạn
+Phân biệt giữa 過程　経過
+過程 : Quá trình, là một bước trong một chuỗi những thay đổi. 生産過程 : quá trình sinh sản
+経過 : Tiến trình, ko chỉ là một bước đơn thuần, nó là cả một loạt những thay đổi dần dần.</t>
+  </si>
+  <si>
+    <t>浄化</t>
+  </si>
+  <si>
+    <t>じょうか - TỊNH HÓA- Làm sạch, thanh tẩy
+浄化データ = dữ liệu đã xóa/che thông tin nhạy cảm (PAN, thẻ, PII...)</t>
+  </si>
+  <si>
+    <t>為</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ため - VI - Bởi vì; mục đích là; Để
+本会員顧客をユニークにする為のID
+ID dùng để phân biệt duy nhất một khách hàng hội viên chính.
+</t>
+  </si>
+  <si>
+    <t>売上受入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うりあげ うけいれ - MẠI THƯỢNG THỤ NHẬP-nhận doanh thu
+=&gt; 売上受入 = quá trình tiếp nhận dữ liệu giao dịch bán hàng vào hệ thống.  </t>
+  </si>
+  <si>
+    <t>払戻し</t>
+  </si>
+  <si>
+    <t>はらいもどし- PHẤT LỆ - hoàn tiền, hoàn trả, refund.</t>
+  </si>
+  <si>
+    <t>誤打</t>
+  </si>
+  <si>
+    <t>ごだ - NGỘ ĐẢ - nhập sai thao tác / nhập nhầm dữ liệu</t>
+  </si>
+  <si>
+    <t>精算</t>
+  </si>
+  <si>
+    <t>せいさん - TINH TOÁN- Đối soát và thanh quyết toán cuối cùng
+精算先加盟店番号: Mã định danh của merchant nhận tiền thanh quyết toán.</t>
+  </si>
+  <si>
+    <t>精算先加盟店番号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">せいさんさき かめいてん ばんごう -TINH TOÁN TIÊN GIA MINH ĐIẾM PHIÊN HÀO - Mã số merchant nhận thanh quyết toán
+加盟店  - Merchant </t>
+  </si>
+  <si>
+    <t>示す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">しめす - KÌ- Biểu hiện ra; chỉ ra; cho thấy/express </t>
+  </si>
+  <si>
+    <t>優待</t>
+  </si>
+  <si>
+    <t>ゆうたい - ƯU ĐÃI- Ưu đãi.</t>
+  </si>
+  <si>
+    <t>累積</t>
+  </si>
+  <si>
+    <t>るいせき - LUY TÍCH- Tích lũy, cộng dồn, lũy kế
+ポイントを累積する期間の月数を設定する。
+→ Thiết lập số tháng của kỳ tích lũy điểm</t>
+  </si>
+  <si>
+    <t>締日</t>
+  </si>
+  <si>
+    <t>しめび - Đế Nhật - ngày chốt</t>
+  </si>
+  <si>
+    <t>累計</t>
+  </si>
+  <si>
+    <t>るいけい - LUY KẾ- Lũy kế; tích luỹ
+累計ポイント điểm tích luỹ</t>
+  </si>
+  <si>
+    <t>マイナス</t>
+  </si>
+  <si>
+    <t>Minus (-), âm, giảm trừ, số âm
+当期度交換可能ポイントがマイナスの場合
+→ Trường hợp điểm có thể đổi trong kỳ hiện tại bị âm.</t>
+  </si>
+  <si>
+    <t>相殺</t>
+  </si>
+  <si>
+    <t>そうさつ - TƯƠNG SÁT- Bù trừ, cấn trừ, offset
+相殺処理 (xử lý bù trừ)</t>
+  </si>
+  <si>
+    <t>債権</t>
+  </si>
+  <si>
+    <t>さいけん - TRÁI QUYỀN- Khoản phải thu, quyền đòi nợ, credit receivable
+カード会社 → 債権者 (chủ nợ)
+会員顧客 → 債務者 (người phải trả nợ)</t>
+  </si>
+  <si>
+    <t>採番</t>
+  </si>
+  <si>
+    <t>さいばん - THẢI PHIÊN- Đánh số, cấp số, gán số định danh tự động
+ポイント種別IDで採番
+→ Sinh số dựa trên Point Type ID</t>
+  </si>
+  <si>
+    <t>グレード</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Grade / Hạng / Cấp bậc
+グレード付与有無フラグ
+→ Cờ xác định có áp dụng cơ chế hạng thành viên hay không.</t>
+  </si>
+  <si>
+    <t>引換</t>
+  </si>
+  <si>
+    <t>ひきかえ - DẪN HOÁN- Đổi lấy, quy đổi, đổi thưởng (redeem/exchange)
+ポイント引換商品管理
+→ Quản lý sản phẩm đổi thưởng.</t>
+  </si>
+  <si>
+    <t>提携</t>
+  </si>
+  <si>
+    <t>ていけい - ĐỀ HUỀ- liên kết, hợp tác
+提携ATM: máy rút tiền có liên kết (rút được tiền ngân hàng không cùng hệ thống)</t>
+  </si>
+  <si>
+    <t>繰越</t>
+  </si>
+  <si>
+    <t>くりこし - SÀO VIỆT-Chuyển sang kỳ sau, carry forward, carry over
+前月繰越金
+Tiền từ tháng trước chuyển sang</t>
+  </si>
+  <si>
+    <t>切替</t>
+  </si>
+  <si>
+    <t>きりかえ - THIẾT THẾ- Chuyển đổi, thay đổi, switch</t>
+  </si>
+  <si>
+    <t>階層</t>
+  </si>
+  <si>
+    <t>かいそう - GIAI TẰNG- Giai tầng; tầng lớp,hierarchy (engineer field), layer</t>
+  </si>
+  <si>
+    <t>細分</t>
+  </si>
+  <si>
+    <t>さいぶん - TẾ PHÂN- Phân nhỏ, chia nhỏ, phân chia chi tiết hơn
+顧客区分を細分する
+→ Phân chia chi tiết hơn các nhóm khách hàng.</t>
+  </si>
+  <si>
+    <t>導出</t>
+  </si>
+  <si>
+    <t>どうしゅつ - ĐẠO XUẤT- Suy ra, tính toán để tạo ra giá trị, derive
+CASE
+ WHEN ...
+ THEN ...
+ ELSE ...
+END
+→ Logic này gọi là 導出ロジック.</t>
+  </si>
+  <si>
+    <t>形態</t>
+  </si>
+  <si>
+    <t>けいたい - HÌNH THÁI- Hình thái; hình thức; dạng; loại hình</t>
+  </si>
+  <si>
+    <t>完済</t>
+  </si>
+  <si>
+    <t>かんさい - HOÀN TẾ- Trả hết nợ, thanh toán toàn bộ dư nợ, Paid off in full</t>
+  </si>
+  <si>
+    <t>遅損金</t>
+  </si>
+  <si>
+    <t>ちそんきん - TRÌ TỔN KIM- khoản tiền phát sinh do khách hàng thanh toán chậm so với thời hạn quy định.</t>
+  </si>
+  <si>
+    <t>元金</t>
+  </si>
+  <si>
+    <t>もときん - NGUYÊN KIM- Tiền vốn; tiền vốn</t>
+  </si>
+  <si>
+    <t>利息</t>
+  </si>
+  <si>
+    <t>りそく - LỢI TỨC- ố tiền lãi thu dc khi đầu tư, gửi ngân hàng ( Đồng/USD/yên)
+金利：lãi xuất bên vay trả ( đơn vị % )
+利子: tiền lãi bên vay trả ( đơn vị Đồng/ yên/ USD)
+VD vay 100万円（元本）×0.03％（金利）=3万円 (利子）
+利回り :　lợi tức/ cổ tức ( khi bạn đầu tư/ gửi ngân hàng thu lời dc % )</t>
+  </si>
+  <si>
+    <t>和暦</t>
+  </si>
+  <si>
+    <t>われき - HÒA LỊCH- Lịch Nhật Bản theo niên hiệu Thiên hoàng (Japanese Era Calendar)</t>
+  </si>
+  <si>
+    <t>外信</t>
+  </si>
+  <si>
+    <t>がいしん - NGOẠI TÍN- Tin tức từ nước ngoài, điện tín/thông tin từ nước ngoài, foreign news dispatch</t>
+  </si>
+  <si>
+    <t>姓</t>
+  </si>
+  <si>
+    <t>かばね - TÍNH- =名字: họ</t>
+  </si>
+  <si>
+    <t>公的</t>
+  </si>
+  <si>
+    <t>こうてき - CÔNG ĐÍCH- Công, chính thức, thuộc cơ quan nhà nước hoặc tổ chức công quyền
+公的機関
+→ Cơ quan công quyền / cơ quan nhà nước.
+公的書類
+→ Giấy tờ chính thức do cơ quan nhà nước cấp.</t>
+  </si>
+  <si>
+    <t>昭和</t>
+  </si>
+  <si>
+    <t>しょうわ  -CHIÊU HÒA- Thời đại Chiêu Hòa 1926–1989</t>
+  </si>
+  <si>
+    <t>リボ使用</t>
+  </si>
+  <si>
+    <t>りぼしよう - Sử dụng hình thức thanh toán Revolving (Revolving Payment)
+hay thường gọi là trả góp vòng quay (リボ払い).
+リボ là gì?
+リボ = リボルビング払い (Revolving Payment)
+Khách hàng không trả toàn bộ dư nợ thẻ mỗi tháng mà trả một khoản cố định hàng tháng.</t>
+  </si>
+  <si>
+    <t>ﾏﾝｽﾘｰｸﾘｱ</t>
+  </si>
+  <si>
+    <t>Monthly Clear -Thanh toán toàn bộ dư nợ phát sinh trong tháng vào kỳ thanh toán tiếp theo.</t>
+  </si>
+  <si>
+    <t>元本</t>
+  </si>
+  <si>
+    <t>げんぽん - NGUYÊN BỔN- Tiền gốc, Vốn gốc ban đầu khi cho vay</t>
+  </si>
+  <si>
+    <t>督促</t>
+  </si>
+  <si>
+    <t>とくそく - ĐỐC XÚC- Sự đốc thúc; sự thúc giục</t>
+  </si>
+  <si>
+    <t>未納</t>
+  </si>
+  <si>
+    <t>みのう - VỊ NẠP- Sự vỡ nợ; sự quá hạn thanh toán; sự chưa thanh toán.</t>
+  </si>
+  <si>
+    <t>返戻</t>
+  </si>
+  <si>
+    <t>へんれい - PHẢN LỆ- Sự trả lại, sự gửi lại, hoàn trả
+借用した本を返戻する。hoàn trả sách đã mượn</t>
+  </si>
+  <si>
+    <t>償却</t>
+  </si>
+  <si>
+    <t>しょうきゃく - THƯỜNG KHƯỚC- Khấu hao ,khấu trừ</t>
+  </si>
+  <si>
+    <t>徴収</t>
+  </si>
+  <si>
+    <t>ちょうしゅう - TRƯNG THU- Thu (thuế, tiền)</t>
+  </si>
+  <si>
+    <t>配偶</t>
+  </si>
+  <si>
+    <t>はいぐう - PHỐI NGẪU- Sự phối ngẫu ( vợ/chồng)
+配偶者：NGƯỜI PHỐI NGẪU( VỢ/CHỒNG)</t>
+  </si>
+  <si>
+    <t>人為</t>
+  </si>
+  <si>
+    <t>じんい - NHÂN VI- yếu tố xuất phát từ hành động của con ngườ</t>
+  </si>
+  <si>
+    <t>フリー入力</t>
+  </si>
+  <si>
+    <t>Free Input - Nhập tự do, nhập thủ công, không bị giới hạn bởi danh sách chọn hoặc code master
+フリー入力可
+→ Cho phép nhập tự do.
+フリー入力項目
+→ Trường nhập tự do.</t>
+  </si>
+  <si>
+    <t>否か</t>
+  </si>
+  <si>
+    <t>いなか - PHỦ- phủ định (của một Danh từ, Tính từ, Động từ nào đó). 
+VD: 美味しいか否か: ngon hay không ngon. 出席するか否か: có mặt hay không có mặt.</t>
   </si>
 </sst>
 </file>
@@ -5274,7 +5624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5291,6 +5641,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5657,7 +6010,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572AC1B0-BE23-45AF-BF40-510643C6C658}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B786"/>
+  <dimension ref="A1:B835"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -7984,7 +8337,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="291" spans="1:2" ht="94.5">
+    <row r="291" spans="1:2" ht="78.75">
       <c r="A291" s="2" t="s">
         <v>582</v>
       </c>
@@ -9241,7 +9594,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="477" spans="1:2" ht="126">
+    <row r="477" spans="1:2" ht="141.75">
       <c r="A477" s="2" t="s">
         <v>877</v>
       </c>
@@ -9449,7 +9802,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="503" spans="1:2" ht="78.75">
+    <row r="503" spans="1:2" ht="94.5">
       <c r="A503" s="2" t="s">
         <v>928</v>
       </c>
@@ -11719,6 +12072,398 @@
       </c>
       <c r="B786" s="1" t="s">
         <v>1494</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" ht="31.5">
+      <c r="A787" s="12" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B787" s="1" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" ht="31.5">
+      <c r="A788" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B788" s="1" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2" ht="141.75">
+      <c r="A789" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" ht="63">
+      <c r="A790" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" ht="78.75">
+      <c r="A791" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" ht="63">
+      <c r="A792" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" ht="31.5">
+      <c r="A793" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" ht="31.5">
+      <c r="A794" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" ht="63">
+      <c r="A795" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B795" s="1" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" ht="78.75">
+      <c r="A796" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B796" s="1" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" ht="31.5">
+      <c r="A797" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B797" s="1" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B798" s="1" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" ht="78.75">
+      <c r="A799" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B799" s="1" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B800" s="1" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" ht="31.5">
+      <c r="A801" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B801" s="1" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" ht="63">
+      <c r="A802" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B802" s="1" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" ht="47.25">
+      <c r="A803" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B803" s="1" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" ht="63">
+      <c r="A804" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B804" s="1" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" ht="63">
+      <c r="A805" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" ht="63">
+      <c r="A806" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" ht="63">
+      <c r="A807" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" ht="63">
+      <c r="A808" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B808" s="1" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" ht="63">
+      <c r="A809" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B809" s="1" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" ht="31.5">
+      <c r="A810" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" ht="31.5">
+      <c r="A811" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B811" s="1" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" ht="78.75">
+      <c r="A812" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B812" s="1" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" ht="126">
+      <c r="A813" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B813" s="1" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" ht="31.5">
+      <c r="A814" s="11" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B814" s="1" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" ht="31.5">
+      <c r="A815" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B815" s="1" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" ht="47.25">
+      <c r="A816" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B816" s="1" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" ht="31.5">
+      <c r="A817" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B817" s="1" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" ht="173.25">
+      <c r="A818" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B818" s="1" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" ht="47.25">
+      <c r="A819" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B819" s="1" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" ht="47.25">
+      <c r="A820" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B820" s="1" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2">
+      <c r="A821" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B821" s="1" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" ht="141.75">
+      <c r="A822" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B822" s="1" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" ht="31.5">
+      <c r="A823" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" ht="157.5">
+      <c r="A824" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B824" s="1" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" ht="47.25">
+      <c r="A825" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B825" s="1" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" ht="31.5">
+      <c r="A826" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B826" s="1" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" ht="31.5">
+      <c r="A827" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B827" s="1" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" ht="31.5">
+      <c r="A828" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B828" s="1" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" ht="63">
+      <c r="A829" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" ht="31.5">
+      <c r="A830" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B830" s="1" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" ht="31.5">
+      <c r="A831" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B831" s="1" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" ht="63">
+      <c r="A832" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B832" s="1" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" ht="31.5">
+      <c r="A833" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B833" s="1" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" ht="110.25">
+      <c r="A834" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" ht="78.75">
+      <c r="A835" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B835" s="1" t="s">
+        <v>1592</v>
       </c>
     </row>
   </sheetData>
